--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/07,26/06,07,26 Останкино КИ/дв 06,07,26 млрсч ост ки.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/07,26/06,07,26 Останкино КИ/дв 06,07,26 млрсч ост ки.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчет Останкино КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\07,26\06,07,26 Останкино КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5C880A7-D22D-4763-92F3-009115269F19}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C9D4D57-1132-49C3-81E3-910A1E8FBF73}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AD$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AD$107</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="147">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -446,6 +446,33 @@
   <si>
     <t>11,07,</t>
   </si>
+  <si>
+    <t>7647  ХОЧУ ВЕТЧ. ИЗ СВИН.ОТРУБА с/н мгс 1/100</t>
+  </si>
+  <si>
+    <t>7651  ХОЧУ ВЕТЧ. МРАМОР. ПМ с/н мгс 1/100_Л11</t>
+  </si>
+  <si>
+    <t>7299  НАБОР ДЛЯ ПИЦЦЫ Папа Может с/к в/у</t>
+  </si>
+  <si>
+    <t>новинка</t>
+  </si>
+  <si>
+    <t>ротация</t>
+  </si>
+  <si>
+    <t>ротация на 1001062507616,ЭКСТРА Папа может с/к с/н в/у 1/100_Л10</t>
+  </si>
+  <si>
+    <t>ротация на 1001061977613,АРОМАТНАЯ с/к с/н в/у 1/100 10шт_Л10</t>
+  </si>
+  <si>
+    <t>ротация на 1001304197608,СЕРВЕЛАТ ШВЕЙЦАРСК.в/к с/н в/у 1/100_Л11</t>
+  </si>
+  <si>
+    <t>плюсом 5 дней</t>
+  </si>
 </sst>
 </file>
 
@@ -465,22 +492,30 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
@@ -1239,7 +1274,7 @@
       </c>
       <c r="T5" s="4">
         <f t="shared" si="0"/>
-        <v>4159</v>
+        <v>5209</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
@@ -1270,7 +1305,7 @@
       <c r="AC5" s="1"/>
       <c r="AD5" s="4">
         <f>SUM(AD6:AD499)</f>
-        <v>2030.2300000000002</v>
+        <v>2180.2300000000005</v>
       </c>
       <c r="AE5" s="1"/>
       <c r="AF5" s="1"/>
@@ -1482,7 +1517,9 @@
       <c r="AB7" s="1">
         <v>4.343</v>
       </c>
-      <c r="AC7" s="1"/>
+      <c r="AC7" s="1" t="s">
+        <v>146</v>
+      </c>
       <c r="AD7" s="1">
         <f t="shared" ref="AD7:AD70" si="7">G7*T7</f>
         <v>0</v>
@@ -1588,7 +1625,9 @@
       <c r="AB8" s="1">
         <v>20.2</v>
       </c>
-      <c r="AC8" s="1"/>
+      <c r="AC8" s="1" t="s">
+        <v>146</v>
+      </c>
       <c r="AD8" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -1803,7 +1842,9 @@
       <c r="AB10" s="1">
         <v>3.0634000000000001</v>
       </c>
-      <c r="AC10" s="1"/>
+      <c r="AC10" s="1" t="s">
+        <v>146</v>
+      </c>
       <c r="AD10" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -2120,7 +2161,9 @@
       <c r="AB13" s="1">
         <v>21.2</v>
       </c>
-      <c r="AC13" s="1"/>
+      <c r="AC13" s="1" t="s">
+        <v>146</v>
+      </c>
       <c r="AD13" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -2330,7 +2373,9 @@
       <c r="AB15" s="1">
         <v>29.6</v>
       </c>
-      <c r="AC15" s="1"/>
+      <c r="AC15" s="1" t="s">
+        <v>146</v>
+      </c>
       <c r="AD15" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -3068,7 +3113,9 @@
       <c r="AB22" s="1">
         <v>40</v>
       </c>
-      <c r="AC22" s="1"/>
+      <c r="AC22" s="1" t="s">
+        <v>146</v>
+      </c>
       <c r="AD22" s="1">
         <f t="shared" si="7"/>
         <v>20.9</v>
@@ -3117,7 +3164,9 @@
       <c r="H23" s="1">
         <v>40</v>
       </c>
-      <c r="I23" s="1"/>
+      <c r="I23" s="1">
+        <v>6008</v>
+      </c>
       <c r="J23" s="1"/>
       <c r="K23" s="1">
         <v>12.8</v>
@@ -4389,8 +4438,8 @@
       <c r="H35" s="1">
         <v>60</v>
       </c>
-      <c r="I35" s="1">
-        <v>6453</v>
+      <c r="I35" s="1" t="s">
+        <v>142</v>
       </c>
       <c r="J35" s="1"/>
       <c r="K35" s="1">
@@ -4446,7 +4495,9 @@
       <c r="AB35" s="1">
         <v>20.399999999999999</v>
       </c>
-      <c r="AC35" s="1"/>
+      <c r="AC35" s="1" t="s">
+        <v>143</v>
+      </c>
       <c r="AD35" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -4495,8 +4546,8 @@
       <c r="H36" s="1">
         <v>60</v>
       </c>
-      <c r="I36" s="1">
-        <v>6454</v>
+      <c r="I36" s="1" t="s">
+        <v>142</v>
       </c>
       <c r="J36" s="1"/>
       <c r="K36" s="1">
@@ -4552,7 +4603,9 @@
       <c r="AB36" s="1">
         <v>24.6</v>
       </c>
-      <c r="AC36" s="1"/>
+      <c r="AC36" s="1" t="s">
+        <v>144</v>
+      </c>
       <c r="AD36" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -4601,8 +4654,8 @@
       <c r="H37" s="1">
         <v>45</v>
       </c>
-      <c r="I37" s="1">
-        <v>6459</v>
+      <c r="I37" s="1" t="s">
+        <v>142</v>
       </c>
       <c r="J37" s="1"/>
       <c r="K37" s="1">
@@ -4659,7 +4712,9 @@
       <c r="AB37" s="1">
         <v>2.8</v>
       </c>
-      <c r="AC37" s="1"/>
+      <c r="AC37" s="1" t="s">
+        <v>145</v>
+      </c>
       <c r="AD37" s="1">
         <f t="shared" si="7"/>
         <v>5.3000000000000007</v>
@@ -7303,7 +7358,9 @@
       <c r="AB62" s="1">
         <v>5.8</v>
       </c>
-      <c r="AC62" s="1"/>
+      <c r="AC62" s="1" t="s">
+        <v>146</v>
+      </c>
       <c r="AD62" s="1">
         <f t="shared" si="7"/>
         <v>8.25</v>
@@ -8269,7 +8326,7 @@
       </c>
       <c r="AC71" s="1"/>
       <c r="AD71" s="1">
-        <f t="shared" ref="AD71:AD104" si="22">G71*T71</f>
+        <f t="shared" ref="AD71:AD107" si="22">G71*T71</f>
         <v>47</v>
       </c>
       <c r="AE71" s="1"/>
@@ -8795,7 +8852,9 @@
       <c r="AB76" s="1">
         <v>4.2</v>
       </c>
-      <c r="AC76" s="1"/>
+      <c r="AC76" s="1" t="s">
+        <v>146</v>
+      </c>
       <c r="AD76" s="1">
         <f t="shared" si="22"/>
         <v>18.920000000000002</v>
@@ -10655,7 +10714,9 @@
       <c r="H94" s="1">
         <v>50</v>
       </c>
-      <c r="I94" s="1"/>
+      <c r="I94" s="1">
+        <v>7333</v>
+      </c>
       <c r="J94" s="1"/>
       <c r="K94" s="1">
         <v>55</v>
@@ -11182,7 +11243,9 @@
       <c r="H99" s="1">
         <v>45</v>
       </c>
-      <c r="I99" s="1"/>
+      <c r="I99" s="1">
+        <v>7489</v>
+      </c>
       <c r="J99" s="1"/>
       <c r="K99" s="1">
         <v>23</v>
@@ -11774,15 +11837,23 @@
       <c r="AV104" s="1"/>
     </row>
     <row r="105" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A105" s="1"/>
-      <c r="B105" s="1"/>
+      <c r="A105" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="C105" s="1"/>
       <c r="D105" s="1"/>
       <c r="E105" s="1"/>
       <c r="F105" s="1"/>
-      <c r="G105" s="7"/>
+      <c r="G105" s="7">
+        <v>0.1</v>
+      </c>
       <c r="H105" s="1"/>
-      <c r="I105" s="1"/>
+      <c r="I105" s="1">
+        <v>7647</v>
+      </c>
       <c r="J105" s="1"/>
       <c r="K105" s="1"/>
       <c r="L105" s="1"/>
@@ -11791,19 +11862,40 @@
       <c r="O105" s="1"/>
       <c r="P105" s="1"/>
       <c r="Q105" s="1"/>
-      <c r="R105" s="1"/>
+      <c r="R105" s="1">
+        <v>0</v>
+      </c>
       <c r="S105" s="1"/>
-      <c r="T105" s="1"/>
+      <c r="T105" s="1">
+        <v>500</v>
+      </c>
       <c r="U105" s="1"/>
       <c r="V105" s="1"/>
-      <c r="W105" s="1"/>
-      <c r="X105" s="1"/>
-      <c r="Y105" s="1"/>
-      <c r="Z105" s="1"/>
-      <c r="AA105" s="1"/>
-      <c r="AB105" s="1"/>
-      <c r="AC105" s="1"/>
-      <c r="AD105" s="1"/>
+      <c r="W105" s="1">
+        <v>0</v>
+      </c>
+      <c r="X105" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y105" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z105" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA105" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB105" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC105" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="AD105" s="1">
+        <f t="shared" si="22"/>
+        <v>50</v>
+      </c>
       <c r="AE105" s="1"/>
       <c r="AF105" s="1"/>
       <c r="AG105" s="1"/>
@@ -11824,15 +11916,23 @@
       <c r="AV105" s="1"/>
     </row>
     <row r="106" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A106" s="1"/>
-      <c r="B106" s="1"/>
+      <c r="A106" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="C106" s="1"/>
       <c r="D106" s="1"/>
       <c r="E106" s="1"/>
       <c r="F106" s="1"/>
-      <c r="G106" s="7"/>
+      <c r="G106" s="7">
+        <v>0.1</v>
+      </c>
       <c r="H106" s="1"/>
-      <c r="I106" s="1"/>
+      <c r="I106" s="1">
+        <v>7651</v>
+      </c>
       <c r="J106" s="1"/>
       <c r="K106" s="1"/>
       <c r="L106" s="1"/>
@@ -11841,19 +11941,40 @@
       <c r="O106" s="1"/>
       <c r="P106" s="1"/>
       <c r="Q106" s="1"/>
-      <c r="R106" s="1"/>
+      <c r="R106" s="1">
+        <v>0</v>
+      </c>
       <c r="S106" s="1"/>
-      <c r="T106" s="1"/>
+      <c r="T106" s="1">
+        <v>500</v>
+      </c>
       <c r="U106" s="1"/>
       <c r="V106" s="1"/>
-      <c r="W106" s="1"/>
-      <c r="X106" s="1"/>
-      <c r="Y106" s="1"/>
-      <c r="Z106" s="1"/>
-      <c r="AA106" s="1"/>
-      <c r="AB106" s="1"/>
-      <c r="AC106" s="1"/>
-      <c r="AD106" s="1"/>
+      <c r="W106" s="1">
+        <v>0</v>
+      </c>
+      <c r="X106" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y106" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z106" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA106" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB106" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC106" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="AD106" s="1">
+        <f t="shared" si="22"/>
+        <v>50</v>
+      </c>
       <c r="AE106" s="1"/>
       <c r="AF106" s="1"/>
       <c r="AG106" s="1"/>
@@ -11874,15 +11995,23 @@
       <c r="AV106" s="1"/>
     </row>
     <row r="107" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A107" s="1"/>
-      <c r="B107" s="1"/>
+      <c r="A107" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="C107" s="1"/>
       <c r="D107" s="1"/>
       <c r="E107" s="1"/>
       <c r="F107" s="1"/>
-      <c r="G107" s="7"/>
+      <c r="G107" s="7">
+        <v>1</v>
+      </c>
       <c r="H107" s="1"/>
-      <c r="I107" s="1"/>
+      <c r="I107" s="1">
+        <v>7299</v>
+      </c>
       <c r="J107" s="1"/>
       <c r="K107" s="1"/>
       <c r="L107" s="1"/>
@@ -11891,19 +12020,40 @@
       <c r="O107" s="1"/>
       <c r="P107" s="1"/>
       <c r="Q107" s="1"/>
-      <c r="R107" s="1"/>
+      <c r="R107" s="1">
+        <v>0</v>
+      </c>
       <c r="S107" s="1"/>
-      <c r="T107" s="1"/>
+      <c r="T107" s="1">
+        <v>50</v>
+      </c>
       <c r="U107" s="1"/>
       <c r="V107" s="1"/>
-      <c r="W107" s="1"/>
-      <c r="X107" s="1"/>
-      <c r="Y107" s="1"/>
-      <c r="Z107" s="1"/>
-      <c r="AA107" s="1"/>
-      <c r="AB107" s="1"/>
-      <c r="AC107" s="1"/>
-      <c r="AD107" s="1"/>
+      <c r="W107" s="1">
+        <v>0</v>
+      </c>
+      <c r="X107" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y107" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z107" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA107" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB107" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC107" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="AD107" s="1">
+        <f t="shared" si="22"/>
+        <v>50</v>
+      </c>
       <c r="AE107" s="1"/>
       <c r="AF107" s="1"/>
       <c r="AG107" s="1"/>
@@ -31524,7 +31674,7 @@
       <c r="AV499" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AD104" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A3:AD107" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
